--- a/tiflow-xborder/build/0.9.0/StructureDefinition-GEM-ERPEU-PR-PAR-EU-GET-Prescription-Input.xlsx
+++ b/tiflow-xborder/build/0.9.0/StructureDefinition-GEM-ERPEU-PR-PAR-EU-GET-Prescription-Input.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4424" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4408" uniqueCount="343">
   <si>
     <t>Property</t>
   </si>
@@ -380,10 +380,6 @@
     <t>closed</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 inv-1:A parameter must have one and only one of (value, resource, part) {(part.exists() and value.empty() and resource.empty()) or (part.empty() and (value.exists() xor resource.exists()))}</t>
   </si>
@@ -424,6 +420,209 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.name</t>
+  </si>
+  <si>
+    <t>Name from the definition</t>
+  </si>
+  <si>
+    <t>The name of the parameter (reference to the operation definition).</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>If parameter is a data type</t>
+  </si>
+  <si>
+    <t>If the parameter is a data type.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inv-1
+</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>If parameter is a whole resource</t>
+  </si>
+  <si>
+    <t>If the parameter is a whole resource.</t>
+  </si>
+  <si>
+    <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.part</t>
+  </si>
+  <si>
+    <t>Named part of a multi-part parameter</t>
+  </si>
+  <si>
+    <t>A named part of a multi-part parameter.</t>
+  </si>
+  <si>
+    <t>Only one level of nested parameters is allowed.</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData</t>
+  </si>
+  <si>
+    <t>requestData</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-1:A parameter must have one and only one of (value, resource, part) {(part.exists() and value.empty() and resource.empty()) or (part.empty() and (value.exists() xor resource.exists()))}workflow-parameters-get-prescription-eu-1:Prescription IDs must be present if the request type is 'e-prescriptions-retrieval' {part.where(name = 'requesttype').value.code = 'e-prescriptions-retrieval' implies part.where(name = 'prescription-id').exists()}</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.part.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.part.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.part.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.part.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.part.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.part.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.part.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:requesttype</t>
+  </si>
+  <si>
+    <t>requesttype</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:requesttype.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:requesttype.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:requesttype.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:requesttype.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:requesttype.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://gematik.de/fhir/erp-eu/ValueSet/GEM_ERPEU_VS_RequestType</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:requesttype.value[x].id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.part.value[x].id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:requestData.part:requesttype.value[x].extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.part.value[x].extension</t>
+  </si>
+  <si>
     <t xml:space="preserve">value:url}
 </t>
   </si>
@@ -432,219 +631,6 @@
   </si>
   <si>
     <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.name</t>
-  </si>
-  <si>
-    <t>Name from the definition</t>
-  </si>
-  <si>
-    <t>The name of the parameter (reference to the operation definition).</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.value[x]</t>
-  </si>
-  <si>
-    <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
-  </si>
-  <si>
-    <t>If parameter is a data type</t>
-  </si>
-  <si>
-    <t>If the parameter is a data type.</t>
-  </si>
-  <si>
-    <t>ele-1
-inv-1</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>If parameter is a whole resource</t>
-  </si>
-  <si>
-    <t>If the parameter is a whole resource.</t>
-  </si>
-  <si>
-    <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inv-1
-</t>
-  </si>
-  <si>
-    <t>Entity. Role, or Act</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.part</t>
-  </si>
-  <si>
-    <t>Named part of a multi-part parameter</t>
-  </si>
-  <si>
-    <t>A named part of a multi-part parameter.</t>
-  </si>
-  <si>
-    <t>Only one level of nested parameters is allowed.</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData</t>
-  </si>
-  <si>
-    <t>requestData</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-1:A parameter must have one and only one of (value, resource, part) {(part.exists() and value.empty() and resource.empty()) or (part.empty() and (value.exists() xor resource.exists()))}workflow-parameters-get-prescription-eu-1:Prescription IDs must be present if the request type is 'e-prescriptions-retrieval' {part.where(name = 'requesttype').value.code = 'e-prescriptions-retrieval' implies part.where(name = 'prescription-id').exists()}</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.resource</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.part.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.part.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.part.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.part.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.part.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part.resource</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.part.resource</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part.part</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.part.part</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:requesttype</t>
-  </si>
-  <si>
-    <t>requesttype</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:requesttype.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:requesttype.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:requesttype.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:requesttype.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:requesttype.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>https://gematik.de/fhir/erp-eu/ValueSet/GEM_ERPEU_VS_RequestType</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:requesttype.value[x].id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.part.value[x].id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:requestData.part:requesttype.value[x].extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.part.value[x].extension</t>
   </si>
   <si>
     <t>Parameters.parameter:requestData.part:requesttype.value[x].system</t>
@@ -2188,24 +2174,24 @@
         <v>77</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>119</v>
-      </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2228,13 +2214,13 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -2285,7 +2271,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -2308,14 +2294,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2334,16 +2320,16 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2381,19 +2367,19 @@
         <v>75</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -2405,7 +2391,7 @@
         <v>75</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>75</v>
@@ -2416,14 +2402,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2442,19 +2428,19 @@
         <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>75</v>
@@ -2503,7 +2489,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2515,21 +2501,21 @@
         <v>75</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2552,17 +2538,15 @@
         <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>75</v>
@@ -2611,7 +2595,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>84</v>
@@ -2634,10 +2618,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2660,13 +2644,13 @@
         <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2717,7 +2701,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -2726,7 +2710,7 @@
         <v>84</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>96</v>
@@ -2735,15 +2719,15 @@
         <v>75</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2766,16 +2750,16 @@
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2825,7 +2809,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2834,7 +2818,7 @@
         <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>75</v>
@@ -2843,15 +2827,15 @@
         <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2877,13 +2861,13 @@
         <v>75</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2933,7 +2917,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2945,7 +2929,7 @@
         <v>75</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>75</v>
@@ -2956,13 +2940,13 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>112</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>75</v>
@@ -3050,24 +3034,24 @@
         <v>77</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>118</v>
+        <v>75</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3090,13 +3074,13 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3147,7 +3131,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3170,14 +3154,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3196,16 +3180,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3243,19 +3227,19 @@
         <v>75</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3267,7 +3251,7 @@
         <v>75</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>75</v>
@@ -3278,14 +3262,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3304,19 +3288,19 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>75</v>
@@ -3365,7 +3349,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3377,21 +3361,21 @@
         <v>75</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3414,17 +3398,15 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -3434,7 +3416,7 @@
         <v>75</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>75</v>
@@ -3473,7 +3455,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>84</v>
@@ -3496,10 +3478,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3522,13 +3504,13 @@
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3579,7 +3561,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3588,7 +3570,7 @@
         <v>84</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>96</v>
@@ -3597,15 +3579,15 @@
         <v>75</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3628,16 +3610,16 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3687,7 +3669,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3696,7 +3678,7 @@
         <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>75</v>
@@ -3705,15 +3687,15 @@
         <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3721,7 +3703,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>77</v>
@@ -3739,13 +3721,13 @@
         <v>75</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3793,7 +3775,7 @@
         <v>117</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3805,7 +3787,7 @@
         <v>75</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>75</v>
@@ -3816,10 +3798,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3842,13 +3824,13 @@
         <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3899,7 +3881,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3922,14 +3904,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -3948,16 +3930,16 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3995,19 +3977,19 @@
         <v>75</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4019,7 +4001,7 @@
         <v>75</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>75</v>
@@ -4030,14 +4012,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4056,19 +4038,19 @@
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>75</v>
@@ -4117,7 +4099,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4129,21 +4111,21 @@
         <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4166,17 +4148,15 @@
         <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>75</v>
@@ -4225,7 +4205,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>84</v>
@@ -4248,10 +4228,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4274,13 +4254,13 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4331,7 +4311,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4340,7 +4320,7 @@
         <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>96</v>
@@ -4349,15 +4329,15 @@
         <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4380,16 +4360,16 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4439,7 +4419,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4448,7 +4428,7 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>75</v>
@@ -4457,15 +4437,15 @@
         <v>75</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4491,13 +4471,13 @@
         <v>75</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4547,7 +4527,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4559,7 +4539,7 @@
         <v>75</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>75</v>
@@ -4570,13 +4550,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>75</v>
@@ -4601,13 +4581,13 @@
         <v>113</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4657,7 +4637,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4669,7 +4649,7 @@
         <v>75</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>75</v>
@@ -4680,10 +4660,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4706,13 +4686,13 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4763,7 +4743,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4786,14 +4766,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4812,16 +4792,16 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4859,19 +4839,19 @@
         <v>75</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -4883,7 +4863,7 @@
         <v>75</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>75</v>
@@ -4894,14 +4874,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4920,19 +4900,19 @@
         <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>75</v>
@@ -4981,7 +4961,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -4993,21 +4973,21 @@
         <v>75</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5030,17 +5010,15 @@
         <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -5050,7 +5028,7 @@
         <v>75</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>75</v>
@@ -5089,7 +5067,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>84</v>
@@ -5112,10 +5090,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5138,13 +5116,13 @@
         <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5171,11 +5149,11 @@
         <v>75</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>75</v>
@@ -5193,7 +5171,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5202,7 +5180,7 @@
         <v>84</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>96</v>
@@ -5211,15 +5189,15 @@
         <v>75</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5242,13 +5220,13 @@
         <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5299,7 +5277,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5322,14 +5300,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5348,16 +5326,16 @@
         <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5395,19 +5373,19 @@
         <v>75</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>131</v>
+        <v>195</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>133</v>
+        <v>197</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5419,7 +5397,7 @@
         <v>75</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>75</v>
@@ -5430,10 +5408,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5459,16 +5437,16 @@
         <v>98</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>75</v>
@@ -5517,7 +5495,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5532,18 +5510,18 @@
         <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5566,16 +5544,16 @@
         <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5625,7 +5603,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5640,18 +5618,18 @@
         <v>96</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5677,14 +5655,14 @@
         <v>104</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>75</v>
@@ -5733,7 +5711,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5748,18 +5726,18 @@
         <v>96</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5782,19 +5760,17 @@
         <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>75</v>
@@ -5843,7 +5819,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -5858,18 +5834,18 @@
         <v>96</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5892,19 +5868,19 @@
         <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="O42" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>75</v>
@@ -5953,7 +5929,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -5968,18 +5944,18 @@
         <v>96</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6002,16 +5978,16 @@
         <v>85</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6061,7 +6037,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6070,7 +6046,7 @@
         <v>84</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>75</v>
@@ -6079,15 +6055,15 @@
         <v>75</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6113,13 +6089,13 @@
         <v>75</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6169,7 +6145,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6181,7 +6157,7 @@
         <v>75</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>75</v>
@@ -6192,13 +6168,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>75</v>
@@ -6223,13 +6199,13 @@
         <v>113</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6279,7 +6255,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6291,7 +6267,7 @@
         <v>75</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>75</v>
@@ -6302,10 +6278,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6328,13 +6304,13 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6385,7 +6361,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6408,14 +6384,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6434,16 +6410,16 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6481,19 +6457,19 @@
         <v>75</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6505,7 +6481,7 @@
         <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>75</v>
@@ -6516,14 +6492,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6542,19 +6518,19 @@
         <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>75</v>
@@ -6603,7 +6579,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6615,21 +6591,21 @@
         <v>75</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6652,17 +6628,15 @@
         <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>75</v>
@@ -6672,7 +6646,7 @@
         <v>75</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>75</v>
@@ -6711,7 +6685,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>84</v>
@@ -6734,10 +6708,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6760,13 +6734,13 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6817,7 +6791,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -6826,7 +6800,7 @@
         <v>84</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>96</v>
@@ -6835,15 +6809,15 @@
         <v>75</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6866,16 +6840,16 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -6925,7 +6899,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -6934,7 +6908,7 @@
         <v>84</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>75</v>
@@ -6943,15 +6917,15 @@
         <v>75</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6977,13 +6951,13 @@
         <v>75</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7033,7 +7007,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7045,7 +7019,7 @@
         <v>75</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>75</v>
@@ -7056,13 +7030,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>75</v>
@@ -7087,13 +7061,13 @@
         <v>113</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7143,7 +7117,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7155,7 +7129,7 @@
         <v>75</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>75</v>
@@ -7166,10 +7140,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7192,13 +7166,13 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7249,7 +7223,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7272,14 +7246,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7298,16 +7272,16 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7345,19 +7319,19 @@
         <v>75</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7369,7 +7343,7 @@
         <v>75</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>75</v>
@@ -7380,14 +7354,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -7406,19 +7380,19 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>75</v>
@@ -7467,7 +7441,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7479,21 +7453,21 @@
         <v>75</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7516,17 +7490,15 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>75</v>
@@ -7536,7 +7508,7 @@
         <v>75</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>75</v>
@@ -7575,7 +7547,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>84</v>
@@ -7598,10 +7570,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7624,13 +7596,13 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7681,7 +7653,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -7690,7 +7662,7 @@
         <v>84</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>96</v>
@@ -7699,15 +7671,15 @@
         <v>75</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7730,16 +7702,16 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -7789,7 +7761,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -7798,7 +7770,7 @@
         <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>75</v>
@@ -7807,15 +7779,15 @@
         <v>75</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7841,13 +7813,13 @@
         <v>75</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -7897,7 +7869,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -7909,7 +7881,7 @@
         <v>75</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>75</v>
@@ -7920,13 +7892,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>75</v>
@@ -7951,13 +7923,13 @@
         <v>113</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8007,7 +7979,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8019,7 +7991,7 @@
         <v>75</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>75</v>
@@ -8030,10 +8002,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8056,13 +8028,13 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8113,7 +8085,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -8136,14 +8108,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8162,16 +8134,16 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8209,19 +8181,19 @@
         <v>75</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -8233,7 +8205,7 @@
         <v>75</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>75</v>
@@ -8244,14 +8216,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8270,19 +8242,19 @@
         <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>75</v>
@@ -8331,7 +8303,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -8343,21 +8315,21 @@
         <v>75</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8380,17 +8352,15 @@
         <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>75</v>
@@ -8400,7 +8370,7 @@
         <v>75</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>75</v>
@@ -8439,7 +8409,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>84</v>
@@ -8462,10 +8432,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8488,13 +8458,13 @@
         <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8521,11 +8491,11 @@
         <v>75</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>75</v>
@@ -8543,7 +8513,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -8552,7 +8522,7 @@
         <v>84</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>96</v>
@@ -8561,15 +8531,15 @@
         <v>75</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8592,13 +8562,13 @@
         <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8649,7 +8619,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -8672,14 +8642,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -8698,16 +8668,16 @@
         <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -8745,19 +8715,19 @@
         <v>75</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>131</v>
+        <v>195</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>133</v>
+        <v>197</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -8769,7 +8739,7 @@
         <v>75</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>75</v>
@@ -8780,10 +8750,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8809,16 +8779,16 @@
         <v>98</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>75</v>
@@ -8828,7 +8798,7 @@
         <v>75</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>75</v>
@@ -8867,7 +8837,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -8882,18 +8852,18 @@
         <v>96</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8916,16 +8886,16 @@
         <v>85</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -8975,7 +8945,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -8990,18 +8960,18 @@
         <v>96</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9027,14 +8997,14 @@
         <v>104</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>75</v>
@@ -9083,7 +9053,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -9098,18 +9068,18 @@
         <v>96</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9132,19 +9102,17 @@
         <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>75</v>
@@ -9193,7 +9161,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -9208,18 +9176,18 @@
         <v>96</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9242,19 +9210,19 @@
         <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="O73" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>75</v>
@@ -9303,7 +9271,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -9318,18 +9286,18 @@
         <v>96</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9352,16 +9320,16 @@
         <v>85</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9411,7 +9379,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -9420,7 +9388,7 @@
         <v>84</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>75</v>
@@ -9429,15 +9397,15 @@
         <v>75</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9463,13 +9431,13 @@
         <v>75</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -9519,7 +9487,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -9531,7 +9499,7 @@
         <v>75</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>75</v>
@@ -9542,13 +9510,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>75</v>
@@ -9573,13 +9541,13 @@
         <v>113</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -9629,7 +9597,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -9641,7 +9609,7 @@
         <v>75</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>75</v>
@@ -9652,10 +9620,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9678,13 +9646,13 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9735,7 +9703,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -9758,14 +9726,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -9784,16 +9752,16 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -9831,19 +9799,19 @@
         <v>75</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -9855,7 +9823,7 @@
         <v>75</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>75</v>
@@ -9866,14 +9834,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -9892,19 +9860,19 @@
         <v>85</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>75</v>
@@ -9953,7 +9921,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -9965,21 +9933,21 @@
         <v>75</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10002,17 +9970,15 @@
         <v>85</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>75</v>
@@ -10022,7 +9988,7 @@
         <v>75</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>75</v>
@@ -10061,7 +10027,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>84</v>
@@ -10084,10 +10050,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10110,13 +10076,13 @@
         <v>85</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10167,7 +10133,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -10176,7 +10142,7 @@
         <v>84</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>96</v>
@@ -10185,15 +10151,15 @@
         <v>75</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10216,16 +10182,16 @@
         <v>85</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -10275,7 +10241,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -10284,7 +10250,7 @@
         <v>84</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>75</v>
@@ -10293,15 +10259,15 @@
         <v>75</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10327,13 +10293,13 @@
         <v>75</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -10383,7 +10349,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -10395,7 +10361,7 @@
         <v>75</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>75</v>
@@ -10406,13 +10372,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>75</v>
@@ -10437,13 +10403,13 @@
         <v>113</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -10493,7 +10459,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -10505,7 +10471,7 @@
         <v>75</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>75</v>
@@ -10516,10 +10482,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10542,13 +10508,13 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10599,7 +10565,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -10622,14 +10588,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -10648,16 +10614,16 @@
         <v>75</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -10695,19 +10661,19 @@
         <v>75</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -10719,7 +10685,7 @@
         <v>75</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>75</v>
@@ -10730,14 +10696,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -10756,19 +10722,19 @@
         <v>85</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>75</v>
@@ -10817,7 +10783,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -10829,21 +10795,21 @@
         <v>75</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10866,17 +10832,15 @@
         <v>85</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>75</v>
@@ -10886,7 +10850,7 @@
         <v>75</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>75</v>
@@ -10925,7 +10889,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>84</v>
@@ -10948,10 +10912,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10974,13 +10938,13 @@
         <v>85</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -11031,7 +10995,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -11040,7 +11004,7 @@
         <v>84</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>96</v>
@@ -11049,15 +11013,15 @@
         <v>75</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11080,16 +11044,16 @@
         <v>85</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11139,7 +11103,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -11148,7 +11112,7 @@
         <v>84</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>75</v>
@@ -11157,15 +11121,15 @@
         <v>75</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11191,13 +11155,13 @@
         <v>75</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -11247,7 +11211,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -11259,7 +11223,7 @@
         <v>75</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>75</v>
@@ -11270,13 +11234,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D92" t="s" s="2">
         <v>75</v>
@@ -11301,13 +11265,13 @@
         <v>113</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11357,7 +11321,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -11369,7 +11333,7 @@
         <v>75</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>75</v>
@@ -11380,10 +11344,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11406,13 +11370,13 @@
         <v>75</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -11463,7 +11427,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -11486,14 +11450,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -11512,16 +11476,16 @@
         <v>75</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -11559,19 +11523,19 @@
         <v>75</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -11583,7 +11547,7 @@
         <v>75</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>75</v>
@@ -11594,14 +11558,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -11620,19 +11584,19 @@
         <v>85</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>75</v>
@@ -11681,7 +11645,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -11693,21 +11657,21 @@
         <v>75</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11730,17 +11694,15 @@
         <v>85</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>75</v>
@@ -11750,7 +11712,7 @@
         <v>75</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>75</v>
@@ -11789,7 +11751,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>84</v>
@@ -11812,10 +11774,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11838,13 +11800,13 @@
         <v>85</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -11871,11 +11833,11 @@
         <v>75</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>75</v>
@@ -11893,7 +11855,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -11902,7 +11864,7 @@
         <v>84</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>96</v>
@@ -11911,15 +11873,15 @@
         <v>75</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11942,13 +11904,13 @@
         <v>75</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L98" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="M98" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -11999,7 +11961,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -12022,14 +11984,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -12048,16 +12010,16 @@
         <v>75</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -12095,19 +12057,19 @@
         <v>75</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>131</v>
+        <v>195</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>133</v>
+        <v>197</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -12119,7 +12081,7 @@
         <v>75</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>75</v>
@@ -12130,10 +12092,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12159,16 +12121,16 @@
         <v>98</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>75</v>
@@ -12217,7 +12179,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -12232,18 +12194,18 @@
         <v>96</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12266,16 +12228,16 @@
         <v>85</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -12325,7 +12287,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
@@ -12340,18 +12302,18 @@
         <v>96</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12377,14 +12339,14 @@
         <v>104</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>75</v>
@@ -12433,7 +12395,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
@@ -12448,18 +12410,18 @@
         <v>96</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12482,19 +12444,17 @@
         <v>85</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>75</v>
@@ -12543,7 +12503,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
@@ -12558,18 +12518,18 @@
         <v>96</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12592,19 +12552,19 @@
         <v>85</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="O104" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>75</v>
@@ -12653,7 +12613,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
@@ -12668,18 +12628,18 @@
         <v>96</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12702,16 +12662,16 @@
         <v>85</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -12761,7 +12721,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -12770,7 +12730,7 @@
         <v>84</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>75</v>
@@ -12779,15 +12739,15 @@
         <v>75</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12813,13 +12773,13 @@
         <v>75</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -12869,7 +12829,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -12881,7 +12841,7 @@
         <v>75</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>75</v>
@@ -12892,13 +12852,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>75</v>
@@ -12923,13 +12883,13 @@
         <v>113</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -12979,7 +12939,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -12991,7 +12951,7 @@
         <v>75</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>75</v>
@@ -13002,10 +12962,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13028,13 +12988,13 @@
         <v>75</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L108" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L108" t="s" s="2">
+      <c r="M108" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -13085,7 +13045,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
@@ -13108,14 +13068,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -13134,16 +13094,16 @@
         <v>75</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -13181,19 +13141,19 @@
         <v>75</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="AC109" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AD109" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>76</v>
@@ -13205,7 +13165,7 @@
         <v>75</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>75</v>
@@ -13216,14 +13176,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -13242,19 +13202,19 @@
         <v>85</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>75</v>
@@ -13303,7 +13263,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -13315,21 +13275,21 @@
         <v>75</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13352,17 +13312,15 @@
         <v>85</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>75</v>
@@ -13372,7 +13330,7 @@
         <v>75</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>75</v>
@@ -13411,7 +13369,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>84</v>
@@ -13434,10 +13392,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13460,13 +13418,13 @@
         <v>85</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -13517,7 +13475,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -13526,7 +13484,7 @@
         <v>84</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>96</v>
@@ -13535,15 +13493,15 @@
         <v>75</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13566,16 +13524,16 @@
         <v>85</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -13625,7 +13583,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>76</v>
@@ -13634,7 +13592,7 @@
         <v>84</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>75</v>
@@ -13643,15 +13601,15 @@
         <v>75</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13677,13 +13635,13 @@
         <v>75</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -13733,7 +13691,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -13745,7 +13703,7 @@
         <v>75</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>75</v>
@@ -13756,13 +13714,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D115" t="s" s="2">
         <v>75</v>
@@ -13787,13 +13745,13 @@
         <v>113</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -13843,7 +13801,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -13855,7 +13813,7 @@
         <v>75</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>75</v>
@@ -13866,10 +13824,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13892,13 +13850,13 @@
         <v>75</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L116" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L116" t="s" s="2">
+      <c r="M116" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -13949,7 +13907,7 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>76</v>
@@ -13972,14 +13930,14 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -13998,16 +13956,16 @@
         <v>75</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L117" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L117" t="s" s="2">
+      <c r="M117" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M117" t="s" s="2">
+      <c r="N117" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -14045,19 +14003,19 @@
         <v>75</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="AC117" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AD117" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE117" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>76</v>
@@ -14069,7 +14027,7 @@
         <v>75</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>75</v>
@@ -14080,14 +14038,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -14106,19 +14064,19 @@
         <v>85</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>75</v>
@@ -14167,7 +14125,7 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
@@ -14179,21 +14137,21 @@
         <v>75</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14216,17 +14174,15 @@
         <v>85</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>75</v>
@@ -14236,7 +14192,7 @@
         <v>75</v>
       </c>
       <c r="S119" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="T119" t="s" s="2">
         <v>75</v>
@@ -14275,7 +14231,7 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>84</v>
@@ -14298,10 +14254,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14324,13 +14280,13 @@
         <v>85</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -14357,11 +14313,11 @@
         <v>75</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="Y120" s="2"/>
       <c r="Z120" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>75</v>
@@ -14379,7 +14335,7 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>76</v>
@@ -14388,7 +14344,7 @@
         <v>84</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>96</v>
@@ -14397,15 +14353,15 @@
         <v>75</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14428,13 +14384,13 @@
         <v>75</v>
       </c>
       <c r="K121" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L121" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L121" t="s" s="2">
+      <c r="M121" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -14485,7 +14441,7 @@
         <v>75</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>76</v>
@@ -14508,14 +14464,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -14534,16 +14490,16 @@
         <v>75</v>
       </c>
       <c r="K122" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L122" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L122" t="s" s="2">
+      <c r="M122" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -14581,19 +14537,19 @@
         <v>75</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>131</v>
+        <v>195</v>
       </c>
       <c r="AC122" t="s" s="2">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="AD122" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>133</v>
+        <v>197</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -14605,7 +14561,7 @@
         <v>75</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>75</v>
@@ -14616,10 +14572,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14645,16 +14601,16 @@
         <v>98</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>75</v>
@@ -14703,7 +14659,7 @@
         <v>75</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>76</v>
@@ -14718,18 +14674,18 @@
         <v>96</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14752,16 +14708,16 @@
         <v>85</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -14811,7 +14767,7 @@
         <v>75</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
@@ -14826,18 +14782,18 @@
         <v>96</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14863,14 +14819,14 @@
         <v>104</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>75</v>
@@ -14919,7 +14875,7 @@
         <v>75</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -14934,18 +14890,18 @@
         <v>96</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14968,19 +14924,17 @@
         <v>85</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>75</v>
@@ -15029,7 +14983,7 @@
         <v>75</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>76</v>
@@ -15044,18 +14998,18 @@
         <v>96</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15078,19 +15032,19 @@
         <v>85</v>
       </c>
       <c r="K127" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="O127" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="L127" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>75</v>
@@ -15139,7 +15093,7 @@
         <v>75</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>76</v>
@@ -15154,18 +15108,18 @@
         <v>96</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15188,16 +15142,16 @@
         <v>85</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -15247,7 +15201,7 @@
         <v>75</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>76</v>
@@ -15256,7 +15210,7 @@
         <v>84</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>75</v>
@@ -15265,15 +15219,15 @@
         <v>75</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15299,13 +15253,13 @@
         <v>75</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -15355,7 +15309,7 @@
         <v>75</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
@@ -15367,7 +15321,7 @@
         <v>75</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>75</v>
